--- a/Configs/GameConfig/Datas/stacklands_equipment.xlsx
+++ b/Configs/GameConfig/Datas/stacklands_equipment.xlsx
@@ -988,7 +988,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>1</v>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="N8" s="29" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>equip-mobs-md-2026-08-06</t>
         </is>
       </c>
       <c r="O8" s="30" t="inlineStr">
         <is>
-          <t>核对日期 2026-08-03</t>
+          <t>2026-08-06 按数值文档：命中 +1 档（Small 60%→Normal 70%）= +10 个百分点</t>
         </is>
       </c>
     </row>
